--- a/artfynd/A 64194-2021 artfynd.xlsx
+++ b/artfynd/A 64194-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64194-2021 artfynd.xlsx
+++ b/artfynd/A 64194-2021 artfynd.xlsx
@@ -23677,7 +23677,7 @@
         <v>112504384</v>
       </c>
       <c r="B192" t="n">
-        <v>90207</v>
+        <v>90217</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>

--- a/artfynd/A 64194-2021 artfynd.xlsx
+++ b/artfynd/A 64194-2021 artfynd.xlsx
@@ -23677,7 +23677,7 @@
         <v>112504384</v>
       </c>
       <c r="B192" t="n">
-        <v>90217</v>
+        <v>90229</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>

--- a/artfynd/A 64194-2021 artfynd.xlsx
+++ b/artfynd/A 64194-2021 artfynd.xlsx
@@ -23677,7 +23677,7 @@
         <v>112504384</v>
       </c>
       <c r="B192" t="n">
-        <v>90229</v>
+        <v>90230</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>

--- a/artfynd/A 64194-2021 artfynd.xlsx
+++ b/artfynd/A 64194-2021 artfynd.xlsx
@@ -23677,7 +23677,7 @@
         <v>112504384</v>
       </c>
       <c r="B192" t="n">
-        <v>90230</v>
+        <v>90233</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>

--- a/artfynd/A 64194-2021 artfynd.xlsx
+++ b/artfynd/A 64194-2021 artfynd.xlsx
@@ -23677,7 +23677,7 @@
         <v>112504384</v>
       </c>
       <c r="B192" t="n">
-        <v>90233</v>
+        <v>90239</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>

--- a/artfynd/A 64194-2021 artfynd.xlsx
+++ b/artfynd/A 64194-2021 artfynd.xlsx
@@ -2939,7 +2939,7 @@
         <v>100196619</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>102607789</v>
       </c>
       <c r="B111" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>102607770</v>
       </c>
       <c r="B112" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>103914680</v>
       </c>
       <c r="B152" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>107814040</v>
       </c>
       <c r="B175" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>110865861</v>
       </c>
       <c r="B178" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>110865827</v>
       </c>
       <c r="B179" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>112508852</v>
       </c>
       <c r="B207" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>112508778</v>
       </c>
       <c r="B208" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
